--- a/data/trans_orig/Hacinamiento_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento_R-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1312</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8224</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1484</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9035</t>
+          <t>8655</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3755</t>
+          <t>4329</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12668</t>
+          <t>13411</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72231</t>
+          <t>72770</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>79150</t>
+          <t>79143</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62602</t>
+          <t>62982</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69647</t>
+          <t>70153</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>139424</t>
+          <t>138681</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>148337</t>
+          <t>147763</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,15%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>665</t>
+          <t>683</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5943</t>
+          <t>6647</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2762</t>
+          <t>2744</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10690</t>
+          <t>10710</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4699</t>
+          <t>4686</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13395</t>
+          <t>13803</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62744</t>
+          <t>62040</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>68022</t>
+          <t>68004</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>56795</t>
+          <t>56775</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>64723</t>
+          <t>64741</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>122777</t>
+          <t>122369</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>131473</t>
+          <t>131486</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>725</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>7115</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1861</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3395</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12329</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,37%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>51506</t>
+          <t>51130</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57462</t>
+          <t>57520</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75860</t>
+          <t>75963</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82638</t>
+          <t>82083</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129860</t>
+          <t>130294</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>138794</t>
+          <t>138833</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12468</t>
+          <t>12389</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>3811</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12218</t>
+          <t>12229</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9356</t>
+          <t>9200</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21544</t>
+          <t>20808</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,95%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>138174</t>
+          <t>138253</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>147129</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>136344</t>
+          <t>136333</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>144730</t>
+          <t>144751</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>277660</t>
+          <t>278396</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>289848</t>
+          <t>290004</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5204</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14235</t>
+          <t>14194</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>8485</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18707</t>
+          <t>18812</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14994</t>
+          <t>15828</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29053</t>
+          <t>29524</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54425</t>
+          <t>54466</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>63456</t>
+          <t>63368</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>79,27%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>65823</t>
+          <t>65718</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>76025</t>
+          <t>76045</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,87%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>124137</t>
+          <t>123666</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>138196</t>
+          <t>137362</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,03%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>89,67%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4268</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13269</t>
+          <t>13700</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>4029</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13376</t>
+          <t>13159</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10554</t>
+          <t>10989</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22619</t>
+          <t>23719</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>16,11%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61601</t>
+          <t>61170</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>70602</t>
+          <t>70281</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59016</t>
+          <t>59233</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>67901</t>
+          <t>68363</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,52%</t>
+          <t>81,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>124643</t>
+          <t>123543</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>136708</t>
+          <t>136273</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,54%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>24799</t>
+          <t>24900</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43228</t>
+          <t>42043</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>33619</t>
+          <t>32699</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53681</t>
+          <t>53374</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62450</t>
+          <t>62230</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>89395</t>
+          <t>88869</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>458332</t>
+          <t>459517</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>476761</t>
+          <t>476660</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,38%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>474868</t>
+          <t>475175</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>494930</t>
+          <t>495850</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>940714</t>
+          <t>941240</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>967659</t>
+          <t>967879</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,96%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>737</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6929</t>
+          <t>7354</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4908</t>
+          <t>4482</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,42 +3423,42 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
+          <t>6,11%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>4409</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>1620</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>9013</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>1,2%</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
           <t>6,69%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>4409</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>2042</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>9178</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54292</t>
+          <t>53867</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60471</t>
+          <t>60484</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68502</t>
+          <t>68928</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,47 +3531,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
+          <t>93,89%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>130222</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>125618</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>133011</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>96,73%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>93,31%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>130222</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>125453</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>132589</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>96,73%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>93,18%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2175</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9976</t>
+          <t>10134</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1952</t>
+          <t>2032</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9211</t>
+          <t>8651</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>12,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>5221</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15348</t>
+          <t>15589</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3801,7 +3801,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>55403</t>
+          <t>55245</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>63204</t>
+          <t>62903</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>59315</t>
+          <t>59875</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>66574</t>
+          <t>66494</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>118557</t>
+          <t>118316</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>128678</t>
+          <t>128684</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4411</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13367</t>
+          <t>12598</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>11295</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8703</t>
+          <t>7998</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21035</t>
+          <t>20213</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,03%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>53156</t>
+          <t>53925</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>62112</t>
+          <t>62694</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56726</t>
+          <t>56669</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65091</t>
+          <t>65162</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>113452</t>
+          <t>114274</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>125784</t>
+          <t>126489</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>94,05%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10457</t>
+          <t>10745</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>22582</t>
+          <t>23495</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10038</t>
+          <t>9565</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22487</t>
+          <t>22880</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>24060</t>
+          <t>22989</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>40682</t>
+          <t>41428</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,91%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>113898</t>
+          <t>112985</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>126023</t>
+          <t>125735</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>138877</t>
+          <t>138484</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>151326</t>
+          <t>151799</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>257162</t>
+          <t>256416</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>273784</t>
+          <t>274855</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5513</t>
+          <t>5368</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15761</t>
+          <t>15159</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8734</t>
+          <t>8446</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21004</t>
+          <t>20039</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>15697</t>
+          <t>16144</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31996</t>
+          <t>30885</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,65%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77690</t>
+          <t>78292</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>87938</t>
+          <t>88083</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,13%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>71004</t>
+          <t>71969</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>83274</t>
+          <t>83562</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>153463</t>
+          <t>154574</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>169762</t>
+          <t>169315</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,3%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3555</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12219</t>
+          <t>12131</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14472</t>
+          <t>14400</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10818</t>
+          <t>10528</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23347</t>
+          <t>23244</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,17%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41692</t>
+          <t>41780</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50251</t>
+          <t>50356</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>59566</t>
+          <t>59638</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>69146</t>
+          <t>69398</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>104602</t>
+          <t>104705</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>117131</t>
+          <t>117421</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,77%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38389</t>
+          <t>39011</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61454</t>
+          <t>60340</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40155</t>
+          <t>39451</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>62544</t>
+          <t>62926</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>82616</t>
+          <t>83606</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>114297</t>
+          <t>114174</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>415511</t>
+          <t>416625</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>438576</t>
+          <t>437954</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>474766</t>
+          <t>474384</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>497155</t>
+          <t>497859</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>899978</t>
+          <t>900101</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>931659</t>
+          <t>930669</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,76%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2105</t>
+          <t>2400</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9731</t>
+          <t>10538</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5138</t>
+          <t>5908</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3033</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12873</t>
+          <t>12108</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,46%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55100</t>
+          <t>54293</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62726</t>
+          <t>62431</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73116</t>
+          <t>72346</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>130212</t>
+          <t>130977</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>139486</t>
+          <t>140052</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2764</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10422</t>
+          <t>11292</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2049</t>
+          <t>1728</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9541</t>
+          <t>9764</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16634</t>
+          <t>16446</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71889</t>
+          <t>71019</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>79547</t>
+          <t>79275</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82880</t>
+          <t>82657</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>90372</t>
+          <t>90693</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>158098</t>
+          <t>158286</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>168816</t>
+          <t>168711</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,55%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9623</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>817</t>
+          <t>717</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6549</t>
+          <t>6810</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>4173</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13175</t>
+          <t>13598</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,34%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39601</t>
+          <t>39687</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47071</t>
+          <t>47117</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,45%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>54462</t>
+          <t>54201</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60194</t>
+          <t>60294</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>97059</t>
+          <t>96636</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>106252</t>
+          <t>106061</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19507</t>
+          <t>19488</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18451</t>
+          <t>19112</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17906</t>
+          <t>18347</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33905</t>
+          <t>34147</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>146290</t>
+          <t>146309</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>157591</t>
+          <t>157627</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>152432</t>
+          <t>151771</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>163618</t>
+          <t>163494</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>302775</t>
+          <t>302533</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>318774</t>
+          <t>318333</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,55%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7267</t>
+          <t>7041</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17120</t>
+          <t>17437</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9096</t>
+          <t>8441</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20351</t>
+          <t>20190</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18008</t>
+          <t>18072</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>33180</t>
+          <t>33332</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>84459</t>
+          <t>84142</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>94312</t>
+          <t>94538</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>78802</t>
+          <t>78963</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>90057</t>
+          <t>90712</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>167552</t>
+          <t>167400</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>182724</t>
+          <t>182660</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>83,47%</t>
+          <t>83,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,0%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1471</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8148</t>
+          <t>8340</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6534</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>3354</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>11679</t>
+          <t>11889</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51481</t>
+          <t>51289</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>58158</t>
+          <t>57861</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>61291</t>
+          <t>61037</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>67161</t>
+          <t>67165</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>115774</t>
+          <t>115564</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>124067</t>
+          <t>124099</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,37%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35753</t>
+          <t>34762</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>57727</t>
+          <t>56732</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28107</t>
+          <t>29264</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49225</t>
+          <t>48765</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>68339</t>
+          <t>67788</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>98708</t>
+          <t>98104</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>465643</t>
+          <t>466638</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>487617</t>
+          <t>488608</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>520322</t>
+          <t>520782</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>541440</t>
+          <t>540283</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>994209</t>
+          <t>994813</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1024578</t>
+          <t>1025129</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2605</t>
+          <t>2522</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>10346</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>1582</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8954</t>
+          <t>8795</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>5538</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16977</t>
+          <t>16237</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93420</t>
+          <t>93381</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>101122</t>
+          <t>101205</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>127078</t>
+          <t>127237</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>134404</t>
+          <t>134450</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>222782</t>
+          <t>223522</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>234430</t>
+          <t>234221</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9016</t>
+          <t>7639</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11128</t>
+          <t>10706</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4444</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15432</t>
+          <t>14543</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>85244</t>
+          <t>86621</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93185</t>
+          <t>93177</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>83637</t>
+          <t>84059</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>92424</t>
+          <t>92550</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>173592</t>
+          <t>174481</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>184580</t>
+          <t>184843</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1790</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8745</t>
+          <t>8324</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9364,7 +9364,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4634</t>
+          <t>4828</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2759</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11019</t>
+          <t>10985</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40675</t>
+          <t>41096</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47630</t>
+          <t>47422</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,7 +9472,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59219</t>
+          <t>59025</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -9487,7 +9487,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>102254</t>
+          <t>102288</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>110514</t>
+          <t>110400</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,46%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4305</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14653</t>
+          <t>15543</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13027</t>
+          <t>12214</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>31144</t>
+          <t>30938</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>18540</t>
+          <t>18359</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>41121</t>
+          <t>41232</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>202373</t>
+          <t>201483</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>212721</t>
+          <t>212579</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>187128</t>
+          <t>187334</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>205245</t>
+          <t>206058</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>394177</t>
+          <t>394066</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>416758</t>
+          <t>416939</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8077</t>
+          <t>8460</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19316</t>
+          <t>20028</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10985</t>
+          <t>10891</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26107</t>
+          <t>25901</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>22251</t>
+          <t>22656</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42039</t>
+          <t>41775</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>99643</t>
+          <t>98931</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>110882</t>
+          <t>110499</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>136510</t>
+          <t>136716</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>151632</t>
+          <t>151726</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>239537</t>
+          <t>239801</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>259325</t>
+          <t>258920</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>91,95%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8845</t>
+          <t>8891</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6326</t>
+          <t>6417</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17433</t>
+          <t>18163</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9906</t>
+          <t>10462</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23653</t>
+          <t>23835</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,92%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>60050</t>
+          <t>60004</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66928</t>
+          <t>66994</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>54570</t>
+          <t>53840</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>65677</t>
+          <t>65586</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>117245</t>
+          <t>117063</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>130992</t>
+          <t>130436</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,57%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28475</t>
+          <t>29011</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49474</t>
+          <t>50213</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>48376</t>
+          <t>47707</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>76622</t>
+          <t>76573</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>82375</t>
+          <t>82549</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>117741</t>
+          <t>117880</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>602812</t>
+          <t>602073</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>623811</t>
+          <t>623275</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>670920</t>
+          <t>670969</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>699166</t>
+          <t>699835</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1282087</t>
+          <t>1281948</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1317453</t>
+          <t>1317279</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
